--- a/load_running_moulds.xlsx
+++ b/load_running_moulds.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,31 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E168"/>
+  <dimension ref="A1:E165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Machine</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SKUCode</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>MouldNos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>MouldLife_remaining</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Num_Moulds</t>
         </is>
@@ -463,16 +451,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1325215613075TTMX0</t>
+          <t>1325216814085SURL0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['C15570R13TAXTLHM02', 'C15570R13TAXTLHM01']</t>
+          <t>['B1658014UXROYLGR14', 'B1658014UXROYLGR07']</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2763</v>
+        <v>1978</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -486,16 +474,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1325218614088TVECE</t>
+          <t>1325220515094VUTR0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['C18570R14VECTLMK04', 'C18570R14VECTLMK02']</t>
+          <t>['B2056515TORINGGC02', 'B2056515TORINGHB01']</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2606</v>
+        <v>2966</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -509,16 +497,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1325215813079STMX0</t>
+          <t>1325220515094VUTR0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['C15580R13TAXIMHM02', 'C15580R13TAXIMHM01']</t>
+          <t>['B2056515TORINGHM02', 'B2056515TORINGHM01']</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2456</v>
+        <v>2992</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -532,16 +520,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1325218515088HUTR0</t>
+          <t>1325217614084HURL2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['B1856515UXTOURGC02', 'B1856515UXTOURGC01']</t>
+          <t>['B1757014UXROYHMI04', 'B1757014UXROYHMI03']</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -564,7 +552,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1385</v>
+        <v>2412</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -578,16 +566,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1325218615089HURL0</t>
+          <t>1225121716010SXC10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>['B1857015UXROYHMI02', 'B1857015UXROYHMI01']</t>
+          <t>['B215/75R16XPC1GC03', 'B215/75R16XPC1GC01']</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2242</v>
+        <v>2758</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -601,16 +589,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1225221615008QXC10</t>
+          <t>1325214813075SUNE1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>['B2157015ULXPC1HM02', 'B2157015ULXPC1HM01']</t>
+          <t>['B1458013ULNEO1GC10', 'B1458013ULNEO1GC09']</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2861</v>
+        <v>290</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -624,16 +612,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1225223516121PSKP0</t>
+          <t>1225221716010SXC10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['B23565R16SKINGGC06', 'B23565R16SKNGHMI01']</t>
+          <t>['B215/75R16XPC1GC02', 'B21575R16XPC1HMI01']</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1583</v>
+        <v>2698</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
@@ -647,16 +635,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1325218615089HURL0</t>
+          <t>1325215813079SUHL0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['B1857015UXROYHMI04', 'B1857015UXROYHMI03']</t>
+          <t>['B1558013ULHLIFHM02', 'B1558013ULHLIFGC01']</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2311</v>
+        <v>1445</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
@@ -670,16 +658,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1225223516121PSKP0</t>
+          <t>1D25215013008SXC11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['B23565R16SKNGHMI03', 'B23565R16SKNGHMI02']</t>
+          <t>['B155R13ULXPC1HMI07', 'B155R13ULXPC1HMI06']</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2765</v>
+        <v>2372</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -693,16 +681,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1325220316094VUX10</t>
+          <t>1325220516095HUTR0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['C20555R16UX1TLGC02', 'C20555R16UX1TLGC01']</t>
+          <t>['B2056516UXTOUHMI02', 'B2056516UXTOURGC01']</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2663</v>
+        <v>1047</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -716,16 +704,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1325214813075SUNE1</t>
+          <t>1325216814085SURL0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['B1458013ULNEO1GC13', 'B1458013ULTNEOGC01']</t>
+          <t>['B1658014UXROYLHM08', 'B1658014UXROYLHM06']</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1794</v>
+        <v>1931</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
@@ -748,7 +736,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>793</v>
+        <v>2724</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -762,16 +750,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1325216814085SURL0</t>
+          <t>1325216814085STMX0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['B1658014UXROYLHM08', 'B1658014UXROYLHM06']</t>
+          <t>['B1658014TAXIMXHM04', 'B1658014TAXIMXGC03']</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>857</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -785,16 +773,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1325221416099WLHP0</t>
+          <t>1225223516121PSKP0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>['B2156016LEVHPHMI02', 'B2156016LEVHPHMI01']</t>
+          <t>['B23565R16SKNGHMI04', 'B23565R16SKINGGC01']</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2982</v>
+        <v>2032</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -803,21 +791,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1325226517112TRAB0</t>
+          <t>1325219416089HRHE0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['B2656517RNAT2HMI02', 'B2656517RNAT2HMI01']</t>
+          <t>['B1956016RNHPEGC04', 'B1956016RNHPEGC01']</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2968</v>
+        <v>2015</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -826,21 +814,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15204</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1325217514082TTMX0</t>
+          <t>1325214813075SUNE1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['B1756514TAXIMXHM04', 'B1756514TAXIMXHM01']</t>
+          <t>['B1458013ULTNEOGC02', 'B1458013ULTNEOGC01']</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1768</v>
+        <v>2559</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -849,21 +837,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>15205</t>
+          <t>15206</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1325214813075SUNE1</t>
+          <t>1325221715100SRHT0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>['B1458013ULNEO1GC17', 'B1458013ULNEO1HM03']</t>
+          <t>['C21575R15RHTTLHM08', 'C21575R15RHTTLHM03']</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1133</v>
+        <v>2222</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -872,21 +860,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>15207</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1325221715100SRHT0</t>
+          <t>1225221716010SXC10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>['C21575R15RHTTLHM08', 'C21575R15RHTTLHM03']</t>
+          <t>['B215/75R16XPC1GC04', 'B21575R16XPC1HMI02']</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1280</v>
+        <v>2703</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
@@ -895,21 +883,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>15208</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1325221416095VURL0</t>
+          <t>1325218515088TURL0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>['B2156016UXROYLGC10', 'B2156016UXROYLGC03']</t>
+          <t>['B1856515UXROYLHM04', 'B1856515UXROYLGC02']</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2992</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -918,7 +906,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>15209</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -932,7 +920,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>798</v>
+        <v>2153</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -941,21 +929,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>15209</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1325218415084TTMX0</t>
+          <t>1325221715100SRHT0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>['C18560R15TAXIMHM03', 'C18560R15TAXIMHM02']</t>
+          <t>['C21575R15RHTTLHM12', 'C21575R15RHTTLHM04']</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2399</v>
+        <v>2292</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -964,21 +952,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15210</t>
+          <t>15211</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1325221715100SRHT0</t>
+          <t>1D25215013008SXC11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>['C21575R15RHTTLHM12', 'C21575R15RHTTLHM04']</t>
+          <t>['B155R13ULXPC1HMI05', 'B155R13ULXPC1HMI03']</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1342</v>
+        <v>1229</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -987,21 +975,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>15211</t>
+          <t>15212</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1325222318102VRHE1</t>
+          <t>1225223516121PSKP0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['B22555R18RHPEHMI02', 'B22555R18RHPEHMI01']</t>
+          <t>['B23565R16SKINGGC05', 'B23565R16SKINGGC04']</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2963</v>
+        <v>2077</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -1010,21 +998,21 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>15212</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1325217415081HUTR0</t>
+          <t>1225223516121PSKP0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>['C17560R15UXTLHMI03', 'C17560R15UXTTHMI02']</t>
+          <t>['B23565R16SKINGGC06', 'B23565R16SKNGHMI03']</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2007</v>
+        <v>2732</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
@@ -1033,21 +1021,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>15213</t>
+          <t>24801</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1325218515088HUTR0</t>
+          <t>1325219316087VUTR0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>['C18565R15UXTTLUZ02', 'C18565R15UXTTLUZ01']</t>
+          <t>['C19555R16UXTTLHM02', 'C19555R16UXTTLHM01']</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1969</v>
+        <v>2968</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
@@ -1056,21 +1044,21 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>24801</t>
+          <t>24802</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1325215513073TUHL0</t>
+          <t>1325214813075SUNE1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['B1556513ULTHILHM02', 'B1556513ULTHILHM01']</t>
+          <t>['B1458013ULNEO1HM10', 'B1458013ULNEO1HM09']</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1662</v>
+        <v>2644</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
@@ -1079,21 +1067,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>24802</t>
+          <t>24803</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1325214813075SUNE1</t>
+          <t>1325219316087VURL0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>['B1458013ULNEO1HM04', 'B1458013ULNEO1HI02']</t>
+          <t>['C19555R16UXRHYHM04', 'B19555R16UXRYLGC01']</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2607</v>
+        <v>2484</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
@@ -1102,21 +1090,21 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>24803</t>
+          <t>24804</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1325215813079STMX0</t>
+          <t>1D25215013008SXC11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>['C15580R13TAXIMHM06', 'C15580R13TAXIMHM04']</t>
+          <t>['C155R13ULTXPC1HM03', 'C155R13ULTXPC1HM02']</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2459</v>
+        <v>777</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
@@ -1125,21 +1113,21 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>24804</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1D25215013008SXC11</t>
+          <t>1325216614081SUTR0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>['C155R13ULTXPC1HM03', 'C155R13ULTXPC1HM02']</t>
+          <t>['C16570R14UXTTLHM02', 'C16570R14UXTTLHM01']</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>2852</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -1148,21 +1136,21 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>24806</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1325216814085SURL0</t>
+          <t>1325215513073TUHL0</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>['B1658014UXROYLGR13', 'B1658014UXROYLGR12']</t>
+          <t>['C15565R13ULTLHMI02', 'C15565R13ULTLHMI01']</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2934</v>
+        <v>961</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
@@ -1171,21 +1159,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>24806</t>
+          <t>24807</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1325217415081HUTR0</t>
+          <t>1D25215013008SXC11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>['C17560R15UXTTHMI01', 'C17560R15UXTLHMI04']</t>
+          <t>['B155R13ULXPC1HMI02', 'B155R13ULXPC1HMI01']</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2017</v>
+        <v>2109</v>
       </c>
       <c r="E33" t="n">
         <v>2</v>
@@ -1194,21 +1182,21 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>24807</t>
+          <t>24808</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1325214813075SUNE1</t>
+          <t>1D25215013008SXC11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>['B1458013ULNEO1GC11', 'B1458013ULNEO1GC04']</t>
+          <t>['C155R13ULTXPC1HM24', 'C155R13ULTXPC1HM01']</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2153</v>
+        <v>2795</v>
       </c>
       <c r="E34" t="n">
         <v>2</v>
@@ -1217,21 +1205,21 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>24808</t>
+          <t>24809</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1D25215013008SXC11</t>
+          <t>1325219316087VURL0</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>['C155R13ULTXPC1HM24', 'C155R13ULTXPC1HM01']</t>
+          <t>['C1955R16UXRHYCHM02', 'C1955R16UXRHYCHM01']</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2091</v>
+        <v>2408</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
@@ -1240,21 +1228,21 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>24809</t>
+          <t>24810</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1325216614081SUTR0</t>
+          <t>1325221417100HURL1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>['C16570R14UXTTLHM03', 'C16570R14UXTTLHM02']</t>
+          <t>['B2156017UXROYLGC04', 'B2156017UXROYLGC03']</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1776</v>
+        <v>2669</v>
       </c>
       <c r="E36" t="n">
         <v>2</v>
@@ -1263,7 +1251,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>24810</t>
+          <t>24811</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1273,11 +1261,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>['B1458013ULNEO1HM09', 'B1458013ULNEO1GC05']</t>
+          <t>['B1458013ULNEO1HM05', 'B1458013ULNEO1HI01']</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1523</v>
+        <v>836</v>
       </c>
       <c r="E37" t="n">
         <v>2</v>
@@ -1286,21 +1274,21 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>24811</t>
+          <t>24812</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1325214813075SUNE1</t>
+          <t>1325216814085SUTR0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['B1458013ULTNEOHM01', 'B1458013ULNEO1HI01']</t>
+          <t>['C16580R14ELZTHM04', 'C16580R14ELZTHM01']</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1123</v>
+        <v>2987</v>
       </c>
       <c r="E38" t="n">
         <v>2</v>
@@ -1309,21 +1297,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>24813</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1325218615089HURL0</t>
+          <t>1325214813075SUNE1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['B1857015UXROYHMI06', 'B1857015UXROYHMI05']</t>
+          <t>['B1458013ULNEO1GC20', 'B1458013ULTNEOHM01']</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2495</v>
+        <v>1556</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
@@ -1332,21 +1320,21 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>24813</t>
+          <t>24814</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1325214813075SUNE1</t>
+          <t>1325215813079STMX0</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['B1458013ULNEO1HM11', 'B1458013ULNEO1GC03']</t>
+          <t>['C15580R13TAXIMHM03', 'C15580R13TAXIMGC01']</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1355</v>
+        <v>1701</v>
       </c>
       <c r="E40" t="n">
         <v>2</v>
@@ -1355,21 +1343,21 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>24814</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1D25115013008QXPC0</t>
+          <t>1325214813075SUNE1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>['B155R13ULTXPCHMI03', 'B155R13ULTXPCHMI01']</t>
+          <t>['B1458013ULNEO1HM12', 'B1458013ULNEO1HM08']</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2797</v>
+        <v>1084</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
@@ -1378,21 +1366,21 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>24815</t>
+          <t>24816</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1325214813075SUNE1</t>
+          <t>1325221715100SRHT0</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>['B1458013ULNEO1HM12', 'B1458013ULNEO1HM08']</t>
+          <t>['C21575R15RHTTLHM02', 'C21575R15RHTTLHM01']</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1148</v>
+        <v>2818</v>
       </c>
       <c r="E42" t="n">
         <v>2</v>
@@ -1401,21 +1389,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>24816</t>
+          <t>24817</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1325214813075SUNE1</t>
+          <t>1325217613082TUNE2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>['B1458013ULNEO1GC10', 'B1458013ULNEO1GC09']</t>
+          <t>['B1757013ULTNEOGC02', 'B1757013ULTNEOGC01']</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>18</v>
+        <v>1425</v>
       </c>
       <c r="E43" t="n">
         <v>2</v>
@@ -1424,21 +1412,21 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>24818</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1325217613082TUNE2</t>
+          <t>1325216614081SUTR0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>['B1757013ULTNEOGC02', 'B1757013ULTNEOGC01']</t>
+          <t>['C16570R14UXTTLHM04', 'C16570R14UXTTLHM03']</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1308</v>
+        <v>2868</v>
       </c>
       <c r="E44" t="n">
         <v>2</v>
@@ -1447,21 +1435,21 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>24818</t>
+          <t>24819</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1325215813079SUHL0</t>
+          <t>1325220516095HUTR0</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>['B1558013ULHLIFGC03', 'B1558013ULHLIFGC02']</t>
+          <t>['B2056516UXTOURGC02', 'B2056516UXTOUHMI01']</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>162</v>
+        <v>1102</v>
       </c>
       <c r="E45" t="n">
         <v>2</v>
@@ -1470,21 +1458,21 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>24819</t>
+          <t>24820</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1D25115013008QXPC0</t>
+          <t>1325219316087VURL0</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>['B155R13ULTIXPCGC02', 'B155R13ULTIXPCGC01']</t>
+          <t>['B19555R16UXRLHMI02', 'B19555R16UXRLHMI01']</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2909</v>
+        <v>717</v>
       </c>
       <c r="E46" t="n">
         <v>2</v>
@@ -1493,21 +1481,21 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>24820</t>
+          <t>24821</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1325217514082TTMX0</t>
+          <t>1D25215013008SXC11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>['B1756514TAXIMXHM06', 'B1756514TAXIMXHM05']</t>
+          <t>['C155R13ULTXPC1HM20', 'C155R13ULTXPC1HM18']</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1804</v>
+        <v>2456</v>
       </c>
       <c r="E47" t="n">
         <v>2</v>
@@ -1516,21 +1504,21 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>24821</t>
+          <t>24822</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1D25215013008SXC11</t>
+          <t>1325215813079SUHL0</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>['C155R13ULTXPC1HM20', 'C155R13ULTXPC1HM18']</t>
+          <t>['B1558013ULHLIFGC03', 'B1558013ULHLIFHM01']</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1761</v>
+        <v>1533</v>
       </c>
       <c r="E48" t="n">
         <v>2</v>
@@ -1539,21 +1527,21 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>24822</t>
+          <t>24824</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1325216614081SUTR0</t>
+          <t>1325217514082HURL2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>['C16570R14UXTTLHM04', 'C16570R14UXTTLHM01']</t>
+          <t>['B17565R14UXROLGC08', 'B17565R14UXROLGC07']</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1725</v>
+        <v>1380</v>
       </c>
       <c r="E49" t="n">
         <v>2</v>
@@ -1562,21 +1550,21 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>24823</t>
+          <t>24825</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1325218515088HUTR0</t>
+          <t>1325221715100SRXT0</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>['B1856515UXTOURGC04', 'B1856515UXTOURGC03']</t>
+          <t>['B2157515RAXATHMI02', 'B2157515RANXATTY01']</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1984</v>
+        <v>2845</v>
       </c>
       <c r="E50" t="n">
         <v>2</v>
@@ -1585,21 +1573,21 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>24826</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1325218614088TVECE</t>
+          <t>1325214813075SUNE1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>['C18570R14VECTLMK03', 'C18570R14VECTLMK01']</t>
+          <t>['B1458013ULNEO1GC08', 'B1458013ULNEO1GC07']</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1529</v>
+        <v>1548</v>
       </c>
       <c r="E51" t="n">
         <v>2</v>
@@ -1608,21 +1596,21 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>24825</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1325214813075SUNE1</t>
+          <t>1D25212812074FXC10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>['B1458013ULNEO1HM07', 'B1458013ULNEO1GC02']</t>
+          <t>['B1208012ULXPC1GC03', 'B1208012ULXPC1GC01']</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1366</v>
+        <v>1015</v>
       </c>
       <c r="E52" t="n">
         <v>2</v>
@@ -1631,21 +1619,21 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>24826</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1325214813075SUNE1</t>
+          <t>1225170015012LSTL0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>['B1458013ULNEO1GC08', 'B1458013ULNEO1GC07']</t>
+          <t>['B70015STKINGLTHM36', 'B70015STKINGLTHM35']</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1388</v>
+        <v>2465</v>
       </c>
       <c r="E53" t="n">
         <v>2</v>
@@ -1654,21 +1642,21 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1325214613071TTMX0</t>
+          <t>1325214812074TUHL0</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>['B1457013TAXIMXHM02', 'B1457013TAXIMXHM01']</t>
+          <t>['B1458012ULHLIFGC04', 'B1458012UHLIFHMI04']</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2591</v>
+        <v>2096</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
@@ -1677,21 +1665,21 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1325119815106QBRQ0</t>
+          <t>1D25213812090FXPC0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>['B1958015BRUTLTHM09', 'B1958015BRUTLTHM08']</t>
+          <t>['B13080R12UXPCHMI07', 'B13080R12UXPCHMI04']</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2490</v>
+        <v>725</v>
       </c>
       <c r="E55" t="n">
         <v>2</v>
@@ -1700,7 +1688,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1710,11 +1698,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>['B1958015BRUTLTHM07', 'B1958015BRTLTHMI01']</t>
+          <t>['B1958015BRTLTHMI03', 'B1958015BRTLTHMI02']</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2495</v>
+        <v>1093</v>
       </c>
       <c r="E56" t="n">
         <v>2</v>
@@ -1723,21 +1711,21 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1D25213812090FXPC0</t>
+          <t>1D25212812074FXC10</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>['B13080R12UXPCHMI07', 'B13080R12UXPCHMI04']</t>
+          <t>['B1208012ULXPC1GC10', 'B1208012ULXPC1GC02']</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>806</v>
+        <v>1035</v>
       </c>
       <c r="E57" t="n">
         <v>2</v>
@@ -1746,21 +1734,21 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1325119815106QBRQ0</t>
+          <t>1D25212812086FXPC0</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>['B1958015BRTLTHMI03', 'B1958015BRTLTHMI02']</t>
+          <t>['B1208012ULXPCHMI09', 'B1208012ULXPCHMI08']</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2512</v>
+        <v>1756</v>
       </c>
       <c r="E58" t="n">
         <v>2</v>
@@ -1769,21 +1757,21 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4408</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1D25212812086FXPC0</t>
+          <t>1325119815106QBRQ0</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>['B1208012ULXPCHMI02', 'B1208012ULXPCHMI01']</t>
+          <t>['B1958015BRUTLTHM06', 'B1958015BRUTLTHM03']</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>2204</v>
       </c>
       <c r="E59" t="n">
         <v>2</v>
@@ -1792,21 +1780,21 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1325217514082TVECH</t>
+          <t>1D25213812090FXPC0</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>['B1756514VECTRAGC04', 'B1756514VECTRAGR03']</t>
+          <t>['B13080R12ULXPCGC02', 'B13080R12UXPCHMI01']</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2684</v>
+        <v>1530</v>
       </c>
       <c r="E60" t="n">
         <v>2</v>
@@ -1815,21 +1803,21 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1325215513073TUHL0</t>
+          <t>1225170015012LSTL0</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>['C15565R13ULTLHMI02', 'C15565R13ULTLHMI01']</t>
+          <t>['B70015STKINGLTHM26', 'B70015STKINGLTGC06']</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1739</v>
+        <v>2315</v>
       </c>
       <c r="E61" t="n">
         <v>2</v>
@@ -1838,21 +1826,21 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1D25213812090FXPC0</t>
+          <t>1325119015008SRBT0</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>['B13080R12ULXPCGC02', 'B13080R12UXPCHMI01']</t>
+          <t>['B19515RANBRUTHMI02', 'B19515RANBRUTHMI01']</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1142</v>
+        <v>2310</v>
       </c>
       <c r="E62" t="n">
         <v>2</v>
@@ -1861,21 +1849,21 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1225221715115SSTL0</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM26', 'B70015STKINGLTGC06']</t>
+          <t>['B2157515STLKNGHM14', 'B2157515STLKGBHM09']</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1583</v>
+        <v>2745</v>
       </c>
       <c r="E63" t="n">
         <v>2</v>
@@ -1884,21 +1872,21 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1325217514082TVECH</t>
+          <t>1225170015012LSTL0</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>['B1756514VECTRAGC07', 'B1756514VECTRAGC06']</t>
+          <t>['B70015STKINGLTHM51', 'B70015STKINGLTHM38']</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2729</v>
+        <v>2885</v>
       </c>
       <c r="E64" t="n">
         <v>2</v>
@@ -1907,7 +1895,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1917,11 +1905,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM47', 'B70015STKINGLTHM33']</t>
+          <t>['B70015STKINGLTHM50', 'B70015STKINGLTHM49']</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1530</v>
+        <v>1283</v>
       </c>
       <c r="E65" t="n">
         <v>2</v>
@@ -1930,21 +1918,21 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1325221715100SRXT0</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM51', 'B70015STKINGLTHM38']</t>
+          <t>['B2157515RAXATHMI03', 'B2157515RAXATHMI01']</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1427</v>
+        <v>2510</v>
       </c>
       <c r="E66" t="n">
         <v>2</v>
@@ -1953,21 +1941,21 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1D25214012006QXC10</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM50', 'B70015STKINGLTHM49']</t>
+          <t>['B14512ULTXPC1HMI02', 'B14512ULTXPC1HMI01']</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2747</v>
+        <v>2987</v>
       </c>
       <c r="E67" t="n">
         <v>2</v>
@@ -1976,21 +1964,21 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1D25213812090FXPC0</t>
+          <t>1325119015008SRBT0</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>['B13080R12UXPCHMI06', 'B13080R12UXPCHMI05']</t>
+          <t>['B19515RANBRUT-HM04', 'B19515RANBRUT-HM03']</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1417</v>
+        <v>2182</v>
       </c>
       <c r="E68" t="n">
         <v>2</v>
@@ -1999,21 +1987,21 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1325121715115SLTB0</t>
+          <t>1225219015010QSTL0</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>['B2157515BRULTHMI04', 'B2157515BRULTHMI03']</t>
+          <t>['B195R15STLKNGHMI02', 'B195R15STLKNGHMI01']</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2933</v>
+        <v>2727</v>
       </c>
       <c r="E69" t="n">
         <v>2</v>
@@ -2022,21 +2010,21 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1225219015010QSTL0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM36', 'B70015STKINGLTHM35']</t>
+          <t>['B195R15STLKNGHMI03', 'B195R15STLKINGHM02']</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2834</v>
+        <v>2754</v>
       </c>
       <c r="E70" t="n">
         <v>2</v>
@@ -2045,21 +2033,21 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1425118916008QRBT0</t>
+          <t>1225170015012LSTL0</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>['B18585R16BRUTEGC08', 'B18585R16BRUTEGC07']</t>
+          <t>['B70015STKINGLTGC01', 'B70015STKINGLTGC13']</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2658</v>
+        <v>2304</v>
       </c>
       <c r="E71" t="n">
         <v>2</v>
@@ -2068,21 +2056,21 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1325217514082TVECH</t>
+          <t>1225170015012LSTL0</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>['B1756514VECTRAGC10', 'B1756514VECTRAGC03']</t>
+          <t>['B70015STKINGLTHM34', 'B70015STKINGLTGC04']</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2646</v>
+        <v>1740</v>
       </c>
       <c r="E72" t="n">
         <v>2</v>
@@ -2091,7 +2079,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2101,11 +2089,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTGC13', 'B70015STKINGLTGC01']</t>
+          <t>['B70015STKINGLTHM18', 'B70015STKINGLTGC05']</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1479</v>
+        <v>2746</v>
       </c>
       <c r="E73" t="n">
         <v>2</v>
@@ -2114,21 +2102,21 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1325119815106QBRQ0</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM21', 'B70015STKINGLTHM07']</t>
+          <t>['B1958015BRUTLTHM07', 'B1958015BRTLTHMI01']</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>260</v>
+        <v>2637</v>
       </c>
       <c r="E74" t="n">
         <v>2</v>
@@ -2137,21 +2125,21 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1325123715105SBRT0</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTGC09', 'B70015STKINGLTGC05']</t>
+          <t>['B2357515BRT4LTHM02', 'B2357515BRT4LTHM01']</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2841</v>
+        <v>1904</v>
       </c>
       <c r="E75" t="n">
         <v>2</v>
@@ -2160,21 +2148,21 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1425118916008QRBT0</t>
+          <t>1225170015012LSTL0</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>['C18585R16BRUTTGR07', 'C18585R16BRUTTGR03']</t>
+          <t>['B70015STKINGLTHM40', 'B70015STKINGLTHM39']</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1691</v>
+        <v>309</v>
       </c>
       <c r="E76" t="n">
         <v>2</v>
@@ -2183,21 +2171,21 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1325121715115SLTB0</t>
+          <t>1325217514082TVECH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>['B2157515BRUTLTDC10', 'B2157515BRUTLTDC09']</t>
+          <t>['B1756514VECTRAGR05', 'B1756514VECTRAGR03']</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2941</v>
+        <v>2789</v>
       </c>
       <c r="E77" t="n">
         <v>2</v>
@@ -2206,7 +2194,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2216,11 +2204,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM40', 'B70015STKINGLTHM39']</t>
+          <t>['B70015STKINGLTHM25', 'B70015STKINGLTHM23']</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1773</v>
+        <v>1659</v>
       </c>
       <c r="E78" t="n">
         <v>2</v>
@@ -2229,21 +2217,21 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1225221715115SSTL0</t>
+          <t>1325123715105SBRT0</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>['B2157515STLKGBHM10', 'B2157515STLKGBHM07']</t>
+          <t>['B2357515BRT4LTHM05', 'B2357515BRT4LTHM04']</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1848</v>
+        <v>2599</v>
       </c>
       <c r="E79" t="n">
         <v>2</v>
@@ -2252,21 +2240,21 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1225121Z14112LSTL0</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTGC17', 'B70015STKINGLTHM16']</t>
+          <t>['B21514STKINGDCDC09', 'B21514STKINGDCDC07']</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>30</v>
+        <v>2476</v>
       </c>
       <c r="E80" t="n">
         <v>2</v>
@@ -2275,21 +2263,21 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1425118916008QRBT0</t>
+          <t>1225121Z14112LSTL0</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>['C18585R16BRUTTDC14', 'C18585R16BRUTTGR06']</t>
+          <t>['B21514STKINGDCDC10', 'B21514STKINGDCDC06']</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2965</v>
+        <v>2464</v>
       </c>
       <c r="E81" t="n">
         <v>2</v>
@@ -2298,21 +2286,21 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1325121715100SBRT0</t>
+          <t>1325213615099MSXT0</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>['B2157515BRT4LTHM04', 'B2157515BRT4LTHM01']</t>
+          <t>['B13570R15STRXTSX03', 'B13570R15STRXTSX05']</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2564</v>
+        <v>2712</v>
       </c>
       <c r="E82" t="n">
         <v>2</v>
@@ -2321,21 +2309,21 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1325121715100SBRT0</t>
+          <t>1325213615099MSXT0</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>['B2157515BRT4LTHM02', 'B2157515BRT4LTHM03']</t>
+          <t>['B13570R15STRXTHM03', 'B13570R15STRXTSX06']</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2663</v>
+        <v>2845</v>
       </c>
       <c r="E83" t="n">
         <v>2</v>
@@ -2344,21 +2332,21 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1325213612065SULX1</t>
+          <t>1325213615099MSXT0</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>['C13570R12ULLXTGR05', 'C13570R12ULLXTGR04']</t>
+          <t>['B13570R15STRXTSX02', 'B13570R15STRXTHM01']</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2554</v>
+        <v>1692</v>
       </c>
       <c r="E84" t="n">
         <v>2</v>
@@ -2367,21 +2355,21 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1325213612065SULX1</t>
+          <t>1225170015012LSTL0</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>['C13570R12ULLXTGR03', 'C13570R12ULLXTGR02']</t>
+          <t>['B70015STKINGLTHM42', 'B70015STKINGLTHM37']</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>999</v>
+        <v>730</v>
       </c>
       <c r="E85" t="n">
         <v>2</v>
@@ -2390,21 +2378,21 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1325217413077TUSP0</t>
+          <t>1225170015012LSTL0</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>['B1756013ULSPRTGC02', 'B1756013ULSPRTGR01']</t>
+          <t>['B70015STKINGLHMI18', 'B70015STKINGLTHM09']</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2621</v>
+        <v>1053</v>
       </c>
       <c r="E86" t="n">
         <v>2</v>
@@ -2413,21 +2401,21 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1325119815106QBRQ0</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM42', 'B70015STKINGLTHM37']</t>
+          <t>['B1958015BRUTLTHM09', 'B1958015BRUTLTHM08']</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2155</v>
+        <v>2504</v>
       </c>
       <c r="E87" t="n">
         <v>2</v>
@@ -2436,7 +2424,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2446,11 +2434,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>['B70015STKINGLHMI18', 'B70015STKINGLTHM09']</t>
+          <t>['B70015STKINGLTGC17', 'B70015STKINGLTGC11']</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>2473</v>
+        <v>1752</v>
       </c>
       <c r="E88" t="n">
         <v>2</v>
@@ -2459,21 +2447,21 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1325119815106QBRQ0</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM18', 'B70015STKINGLTHM10']</t>
+          <t>['B1958015BRUTLTHM05', 'B1958015BRUTLTHM04']</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1524</v>
+        <v>1915</v>
       </c>
       <c r="E89" t="n">
         <v>2</v>
@@ -2482,7 +2470,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>4922</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2492,11 +2480,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTGC04', 'B70015STKINGLTHM34']</t>
+          <t>['B70015STKINGLTHM28', 'B70015STKINGLTGC20']</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>119</v>
+        <v>1486</v>
       </c>
       <c r="E90" t="n">
         <v>2</v>
@@ -2505,21 +2493,21 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1325217413077TUSP0</t>
+          <t>1325217514082TVECH</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>['B1756013ULSPRTGR02', 'B1756013ULSPRTGC01']</t>
+          <t>['B1756514VECTRAGC12', 'B1756514VECTRAGC09']</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2741</v>
+        <v>2878</v>
       </c>
       <c r="E91" t="n">
         <v>2</v>
@@ -2528,21 +2516,21 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1325217613082TUNE0</t>
+          <t>1225170015012LSTL0</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>['C17570R13ULNTLGC04', 'C17570R13ULNTLGC03']</t>
+          <t>['B70015STKINGLHMI20', 'B70015STKINGLHMI19']</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2698</v>
+        <v>2085</v>
       </c>
       <c r="E92" t="n">
         <v>2</v>
@@ -2551,7 +2539,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2561,11 +2549,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM28', 'B70015STKINGLTGC20']</t>
+          <t>['B70015STKINGLTHM45', 'B70015STKINGLTHM44']</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2907</v>
+        <v>2303</v>
       </c>
       <c r="E93" t="n">
         <v>2</v>
@@ -2574,21 +2562,21 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>54801</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1225170015010LSTL0</t>
+          <t>1325218515088HUTR0</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTGC19', 'B70015STKINGLTHM12']</t>
+          <t>['C18565R15UXTTLUZ02', 'C18565R15UXTTLUZ01']</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1915</v>
+        <v>2255</v>
       </c>
       <c r="E94" t="n">
         <v>2</v>
@@ -2597,21 +2585,21 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>54802</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1325217613082TUNE0</t>
+          <t>1325218515088HTMX0</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>['C17570R13ULNTLGC06', 'C17570R13ULNTLGC05']</t>
+          <t>['B18565R15TAXMHMI04', 'B18565R15TAXMHMI03']</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1828</v>
+        <v>1680</v>
       </c>
       <c r="E95" t="n">
         <v>2</v>
@@ -2620,21 +2608,21 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>54803</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1325216614081STMX0</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM45', 'B70015STKINGLTHM44']</t>
+          <t>['B1657014TAXIMXGC04', 'B1657014TAXIMXGC03']</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1033</v>
+        <v>1667</v>
       </c>
       <c r="E96" t="n">
         <v>2</v>
@@ -2643,21 +2631,21 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>54801</t>
+          <t>54804</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1325218415084TTMX0</t>
+          <t>1325216814085SUTR0</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>['B18560R15TAXIMHM06', 'C18560R15TAXIMHM01']</t>
+          <t>['C16580R14ELZTGC06', 'C16580R14ELZTHM02']</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2648</v>
+        <v>2966</v>
       </c>
       <c r="E97" t="n">
         <v>2</v>
@@ -2666,21 +2654,21 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>54802</t>
+          <t>75201</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1325215613075TTMX0</t>
+          <t>1325217514082HURL2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>['B15570R13TAXTLGC02', 'B15570R13TAXTLGC01']</t>
+          <t>['B17565R14UXROLGC02', 'B17565R14UXROLGC01']</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2757</v>
+        <v>1370</v>
       </c>
       <c r="E98" t="n">
         <v>2</v>
@@ -2689,21 +2677,21 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>54803</t>
+          <t>75202</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1325216614081STMX0</t>
+          <t>1325219416089HRHE0</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>['B1657014TAXIMXGC04', 'B1657014TAXIMXGC03']</t>
+          <t>['B1956016RNHPEGC03', 'B1956016RNHPEGC02']</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1529</v>
+        <v>2216</v>
       </c>
       <c r="E99" t="n">
         <v>2</v>
@@ -2712,21 +2700,21 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>54804</t>
+          <t>75203</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1325216614081STMX0</t>
+          <t>1325214813075SUNE1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>['C16570R14TAXTLHM02', 'C16570R14TAXTLHM01']</t>
+          <t>['B1458013ULNEO1HM11', 'B1458013ULNEO1GC03']</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>1567</v>
       </c>
       <c r="E100" t="n">
         <v>2</v>
@@ -2735,21 +2723,21 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>75201</t>
+          <t>75204</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1325218515088HTMX0</t>
+          <t>1325221417100HURL1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>['B18565R15TAXMHMI04', 'B18565R15TAXMHMI03']</t>
+          <t>['C21560R17UXRTLHM05', 'B2156017UXROYLGC05']</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>105</v>
+        <v>2861</v>
       </c>
       <c r="E101" t="n">
         <v>2</v>
@@ -2758,21 +2746,21 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>75202</t>
+          <t>75205</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1325221416095VURL0</t>
+          <t>1325219416089HRHE0</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>['B2156016UXROYLGC18', 'B2156016UXROYLGC06']</t>
+          <t>['B1956016RNHPEHMI02', 'B1956016RNHPEHMI01']</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>2216</v>
       </c>
       <c r="E102" t="n">
         <v>2</v>
@@ -2781,21 +2769,21 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>75203</t>
+          <t>75206</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1325214813075SUNE1</t>
+          <t>1325217613082TUNE2</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>['B1458013ULNEO1GC12', 'B1458013ULNEO1GC06']</t>
+          <t>['B1757013ULTNEOGC04', 'B1757013ULTNEOGC03']</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1425</v>
+        <v>830</v>
       </c>
       <c r="E103" t="n">
         <v>2</v>
@@ -2804,21 +2792,21 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>75204</t>
+          <t>75207</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1325218515088HTMX0</t>
+          <t>1325219415088VURL1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>['B18565R15TAXMHMI02', 'B18565R15TAXMHMI01']</t>
+          <t>['B1956015UXROYLGC02', 'B1956015UXROYLGC01']</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>538</v>
+        <v>2966</v>
       </c>
       <c r="E104" t="n">
         <v>2</v>
@@ -2827,21 +2815,21 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>75205</t>
+          <t>75208</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1325221416095VURL0</t>
+          <t>1325221417100HURL1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>['B2156016UXROYLGC09', 'B2156016UXROYLGC07']</t>
+          <t>['B2156017UXROYLGC06', 'B2156017UXROYLGC02']</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1316</v>
+        <v>1924</v>
       </c>
       <c r="E105" t="n">
         <v>2</v>
@@ -2850,21 +2838,21 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>75206</t>
+          <t>75209</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1325217514082TTMX0</t>
+          <t>1325214813075SUNE1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>['B1756514TAXIMXHM02', 'B1756514TAXIMXGC01']</t>
+          <t>['B1458013ULNEO1GC15', 'B1458013ULTNEOHM02']</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2731</v>
+        <v>1615</v>
       </c>
       <c r="E106" t="n">
         <v>2</v>
@@ -2873,21 +2861,21 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>75207</t>
+          <t>75210</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1D25115013008QXPC0</t>
+          <t>1325217614084HURL2</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>['B155R13ULTXPCHMI04', 'B155R13ULTXPCHMI02']</t>
+          <t>['B1757014UXROYBGC02', 'B1757014UXROYBGC01']</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>2601</v>
+        <v>2255</v>
       </c>
       <c r="E107" t="n">
         <v>2</v>
@@ -2896,21 +2884,21 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>75208</t>
+          <t>75211</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1325221715100SRHT0</t>
+          <t>1325218515088HTMX0</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>['C21575R15RHTTLHM15', 'C21575R15RHTTLHM09']</t>
+          <t>['C18565R15TAXIMHM04', 'C18565R15TAXIMHM02']</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2070</v>
+        <v>544</v>
       </c>
       <c r="E108" t="n">
         <v>2</v>
@@ -2919,21 +2907,21 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>75209</t>
+          <t>75212</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1325214813075SUNE1</t>
+          <t>1325222417099HURL0</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>['B1458013ULNEO1GC20', 'B1458013ULTNEOHM02']</t>
+          <t>['C22560R17UXRHB02', 'B22560R17UXRYLGC02']</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1217</v>
+        <v>2402</v>
       </c>
       <c r="E109" t="n">
         <v>2</v>
@@ -2942,21 +2930,21 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>75210</t>
+          <t>75213</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1325217614084HURL2</t>
+          <t>1325218515088HTMX0</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>['B1757014UXROYBGC02', 'B1757014UXROYBGC01']</t>
+          <t>['C18565R15TAXIMHM03', 'C18565R15TAXIMGC02']</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1475</v>
+        <v>2441</v>
       </c>
       <c r="E110" t="n">
         <v>2</v>
@@ -2965,21 +2953,21 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>75211</t>
+          <t>75214</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1325218515088HTMX0</t>
+          <t>1325221416095VURL0</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>['C18565R15TAXIMHM04', 'C18565R15TAXIMHM02']</t>
+          <t>['B2156016UXROYLGC15', 'B2156016UXROYLGC09']</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2088</v>
+        <v>2797</v>
       </c>
       <c r="E111" t="n">
         <v>2</v>
@@ -2988,21 +2976,21 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>75212</t>
+          <t>75215</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1325221417100HURL1</t>
+          <t>1325214813075SUNE1</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>['C21560R17UXRTLHM11', 'C21560R17UXRTLHM07']</t>
+          <t>['B1458013ULNEO1HM04', 'B1458013ULNEO1HI02']</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1613</v>
+        <v>154</v>
       </c>
       <c r="E112" t="n">
         <v>2</v>
@@ -3011,21 +2999,21 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>75213</t>
+          <t>75216</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1325218515088HTMX0</t>
+          <t>1325221715100SRHT0</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>['C18565R15TAXIMHM03', 'C18565R15TAXIMGC02']</t>
+          <t>['C21575R15RHTTLHM15', 'C21575R15RHTTLHM09']</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2192</v>
+        <v>1821</v>
       </c>
       <c r="E113" t="n">
         <v>2</v>
@@ -3034,21 +3022,21 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>75214</t>
+          <t>75217</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1325223517104HRHT0</t>
+          <t>1325221416095VURL0</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>['B23565R17RHTTLHM09', 'C23565R17RHTTLHM02']</t>
+          <t>['B2156016UXROYLGC16', 'B2156016UXROYLGC05']</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2972</v>
+        <v>260</v>
       </c>
       <c r="E114" t="n">
         <v>2</v>
@@ -3057,21 +3045,21 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>75215</t>
+          <t>75218</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1325214813075SUNE1</t>
+          <t>1325218515088HTMX0</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>['B1458013ULNEO1GC15', 'B1458013ULNEO1HM05']</t>
+          <t>['C18565R15TAXIMHM08', 'C18565R15TAXIMHM05']</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>2650</v>
       </c>
       <c r="E115" t="n">
         <v>2</v>
@@ -3080,21 +3068,21 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>75216</t>
+          <t>75219</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1325221417100HURL1</t>
+          <t>1325221416095VURL0</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>['B2156017UXROYLGC06', 'B2156017UXROYLGC02']</t>
+          <t>['B2156016UXROYLGC07', 'B2156016UXROYLGC01']</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1226</v>
+        <v>2706</v>
       </c>
       <c r="E116" t="n">
         <v>2</v>
@@ -3103,21 +3091,21 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>75217</t>
+          <t>75220</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1325221416095VURL0</t>
+          <t>1325214813075SUNE1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>['B2156016UXROYLGC16', 'B2156016UXROYLGC05']</t>
+          <t>['B1458013ULNEO1GC13', 'B1458013ULNEO1GC05']</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2899</v>
+        <v>2743</v>
       </c>
       <c r="E117" t="n">
         <v>2</v>
@@ -3126,21 +3114,21 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>75218</t>
+          <t>75221</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1325218515088HTMX0</t>
+          <t>1325226517112HRHT0</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>['C18565R15TAXIMHM08', 'C18565R15TAXIMHM05']</t>
+          <t>['C26565R17RHTTLGC02', 'C26565R17RHTTLGC01']</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2370</v>
+        <v>2522</v>
       </c>
       <c r="E118" t="n">
         <v>2</v>
@@ -3149,21 +3137,21 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>75219</t>
+          <t>75222</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1325221416095VURL0</t>
+          <t>1325218614088HURL0</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>['B2156016UXROYLGC02', 'B2156016UXROYLGC01']</t>
+          <t>['B1857014UXROYLMK01', 'B1857014UXROYLHB01']</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2510</v>
+        <v>2180</v>
       </c>
       <c r="E119" t="n">
         <v>2</v>
@@ -3172,21 +3160,21 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>75220</t>
+          <t>75223</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1325216514079TTMX0</t>
+          <t>1325221417100HURL1</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>['C16565R14TAXIMHM02', 'C16565R14TAXIMHM01']</t>
+          <t>['C21560R17UXRTLHM08', 'B2156017UXROYLGC01']</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2817</v>
+        <v>2518</v>
       </c>
       <c r="E120" t="n">
         <v>2</v>
@@ -3195,17 +3183,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>75221</t>
+          <t>75224</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1325223517104HRHT0</t>
+          <t>1325218515088HTMX0</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>['C23565R17RHTTLGC02', 'C23565R17RHTTLGC01']</t>
+          <t>['C18565R15TAXIMHM07', 'C18565R15TAXIMHM06']</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -3218,21 +3206,21 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>75222</t>
+          <t>75225</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1325218415088VLHP0</t>
+          <t>1325221416095VURL0</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>['B1856015LEVHPHMI02', 'B1856015LEVHPHMI01']</t>
+          <t>['B2156016UXROYLGC12', 'B2156016UXROYLGC08']</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2955</v>
+        <v>119</v>
       </c>
       <c r="E122" t="n">
         <v>2</v>
@@ -3241,21 +3229,21 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>75223</t>
+          <t>75226</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1325221417100HURL1</t>
+          <t>1325217514082HURL2</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>['C21560R17UXRTLHM08', 'B2156017UXROYLGC01']</t>
+          <t>['B17565R14UXROLGC04', 'B17565R14UXROLGC03']</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1816</v>
+        <v>1505</v>
       </c>
       <c r="E123" t="n">
         <v>2</v>
@@ -3264,21 +3252,21 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>75224</t>
+          <t>75227</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1325218515088HTMX0</t>
+          <t>1325221416095VURL0</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>['C18565R15TAXIMHM07', 'C18565R15TAXIMHM06']</t>
+          <t>['B2156016UXROYLGC06', 'B2156016UXROYLGC03']</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2218</v>
+        <v>2643</v>
       </c>
       <c r="E124" t="n">
         <v>2</v>
@@ -3287,21 +3275,21 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>75225</t>
+          <t>75228</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1325221416095VURL0</t>
+          <t>1325216814085SURL0</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>['B2156016UXROYLGC12', 'B2156016UXROYLGC08']</t>
+          <t>['B1658014UXROYLHM19', 'B1658014UXROYLHM12']</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2609</v>
+        <v>263</v>
       </c>
       <c r="E125" t="n">
         <v>2</v>
@@ -3310,21 +3298,21 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>75226</t>
+          <t>75229</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1325214613071TTMX0</t>
+          <t>1325218515088TURL0</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>['B1457013TAXMXHMI04', 'B1457013TAXMXHMI03']</t>
+          <t>['B1856515UXROYLHM03', 'B1856515UXROYLGC01']</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>2603</v>
+        <v>2991</v>
       </c>
       <c r="E126" t="n">
         <v>2</v>
@@ -3333,21 +3321,21 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>75227</t>
+          <t>75230</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1325217614084HURL2</t>
+          <t>1325219316087VUTR0</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>['B1757014UXROYHMI04', 'B1757014UXROYHMI03']</t>
+          <t>['B19555R16UXTTHMI02', 'B19555R16UXTTHMI01']</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1298</v>
+        <v>2961</v>
       </c>
       <c r="E127" t="n">
         <v>2</v>
@@ -3356,21 +3344,21 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>75228</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1325217514082HURL2</t>
+          <t>1225170015012LSTL0</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>['B17565R14UXROLGC08', 'B17565R14UXROLGC07']</t>
+          <t>['V700R15STLKNG-SX02', 'V700R15STLKNG-SX01']</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2548</v>
+        <v>2980</v>
       </c>
       <c r="E128" t="n">
         <v>2</v>
@@ -3379,21 +3367,21 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>75229</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1325217514082TTMX0</t>
+          <t>1225221715115SSTL0</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>['B1756514TAXIMXGC02', 'B1756514TAXIMXHM03']</t>
+          <t>['B2157515STLKGHMI02', 'B2157515STLKGHMI01']</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>2115</v>
+        <v>2596</v>
       </c>
       <c r="E129" t="n">
         <v>2</v>
@@ -3402,21 +3390,21 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>75230</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1325216614081STMX0</t>
+          <t>1225221715115SSTL0</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>['C16570R14TAXTLGC02', 'C16570R14TAXTLGC01']</t>
+          <t>['B2157515STLKNGHM12', 'B2157515STLKNGHM11']</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>2470</v>
+        <v>346</v>
       </c>
       <c r="E130" t="n">
         <v>2</v>
@@ -3425,7 +3413,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3435,11 +3423,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM25', 'B70015STKINGLTHM23']</t>
+          <t>['B70015STKINGLTGC12', 'B70015STKINGLTGC08']</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>1371</v>
       </c>
       <c r="E131" t="n">
         <v>2</v>
@@ -3448,21 +3436,21 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1225221715115SSTL0</t>
+          <t>1225170015012LSTL0</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>['B2157515STLKNGHM13', 'B2157515STLKGHMI05']</t>
+          <t>['B70015STKINGLTHM15', 'B70015STKINGLTHM16']</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>455</v>
+        <v>1706</v>
       </c>
       <c r="E132" t="n">
         <v>2</v>
@@ -3471,7 +3459,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3481,11 +3469,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>['B2157515STLKNGHM12', 'B2157515STLKNGHM11']</t>
+          <t>['B2157515STLKGHMI06', 'B2157515STLKGHMI03']</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1708</v>
+        <v>2060</v>
       </c>
       <c r="E133" t="n">
         <v>2</v>
@@ -3494,7 +3482,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3504,11 +3492,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTGC12', 'B70015STKINGLTGC08']</t>
+          <t>['B70015STKINGLHMI17', 'B70015STKINGLTHM07']</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>2829</v>
+        <v>1918</v>
       </c>
       <c r="E134" t="n">
         <v>2</v>
@@ -3517,21 +3505,21 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1325218614088HURL0</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTSY02', 'B70015STKINGLTSY01']</t>
+          <t>['B1857014UXROYLHB02', 'B1857014UXROYLMK02']</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>2836</v>
+        <v>2965</v>
       </c>
       <c r="E135" t="n">
         <v>2</v>
@@ -3540,7 +3528,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3550,11 +3538,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM15', 'B70015STKINGLTGC11']</t>
+          <t>['B70015STKINGLTGC10', 'B70015STKINGLTGC07']</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>89</v>
+        <v>828</v>
       </c>
       <c r="E136" t="n">
         <v>2</v>
@@ -3563,21 +3551,21 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1225221715115SSTL0</t>
+          <t>1325217514082TVECH</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>['B2157515STLKGHMI06', 'B2157515STLKGHMI03']</t>
+          <t>['B1756514VECTRAGC04', 'B1756514VECTRAGC03']</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>2217</v>
+        <v>2801</v>
       </c>
       <c r="E137" t="n">
         <v>2</v>
@@ -3586,21 +3574,21 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1325215813079SUHL0</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM43', 'B70015STKINGLTHM41']</t>
+          <t>['B1558013ULHLIFGC04', 'B1558013ULHLIFGC02']</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2251</v>
+        <v>2256</v>
       </c>
       <c r="E138" t="n">
         <v>2</v>
@@ -3609,21 +3597,21 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1D25212812074FXC10</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTGC10', 'B70015STKINGLTGC07']</t>
+          <t>['B1208012ULXPC1GC08', 'B1208012ULXPC1GC07']</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2228</v>
+        <v>441</v>
       </c>
       <c r="E139" t="n">
         <v>2</v>
@@ -3632,21 +3620,21 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1225170015010LSTL0</t>
+          <t>1225170015012LSTL0</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM14', 'B70015STKINGLTHM13']</t>
+          <t>['B70015STKINGLTHM52', 'B70015STKINGLTHM29']</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2577</v>
+        <v>1420</v>
       </c>
       <c r="E140" t="n">
         <v>2</v>
@@ -3655,21 +3643,21 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9402</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1225221715115SSTL0</t>
+          <t>1325123715105SBRT0</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>['B2157515STLKGHMI02', 'B2157515STLKGHMI01']</t>
+          <t>['B2357515BRT4LTHM06', 'B2357515BRT4LTHM03']</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2060</v>
+        <v>2783</v>
       </c>
       <c r="E141" t="n">
         <v>2</v>
@@ -3678,21 +3666,21 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1D25212812074FXC10</t>
+          <t>1D25212812086FXPC0</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>['B1208012ULXPC1GC08', 'B1208012ULXPC1GC07']</t>
+          <t>['B1208012ULXPCHMI02', 'B1208012ULXPCHMI01']</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>2970</v>
+        <v>1780</v>
       </c>
       <c r="E142" t="n">
         <v>2</v>
@@ -3701,21 +3689,21 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1D25212812086FXPC0</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM52', 'B70015STKINGLTHM29']</t>
+          <t>['B1208012ULTXPCHM01', 'B1208012ULTXPCHM02']</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2553</v>
+        <v>1773</v>
       </c>
       <c r="E143" t="n">
         <v>2</v>
@@ -3724,21 +3712,21 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1325114812074TUHL0</t>
+          <t>1325119015008SRBT0</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>['B1458012UHLIFHMI03', 'B1458012ULHLIFHM02']</t>
+          <t>['B19515RANBRUTBHM02', 'B19515RANBRUTBHM01']</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1432</v>
+        <v>2218</v>
       </c>
       <c r="E144" t="n">
         <v>2</v>
@@ -3747,21 +3735,21 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1425118916008QRBT0</t>
+          <t>1325214812074TUHL0</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>['C18585R16BRUTTGR08', 'C18585R16BRUTTGR02']</t>
+          <t>['B1458012ULHLIFGC03', 'B1458012ULHLIFHM01']</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2331</v>
+        <v>2055</v>
       </c>
       <c r="E145" t="n">
         <v>2</v>
@@ -3770,21 +3758,21 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>9404</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1D25214012008QSTL0</t>
+          <t>1325215813079STMX0</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>['B14512STKINGLTGC02', 'B14512STKINGLTGC01']</t>
+          <t>['C15580R13TAXIMGC02', 'C15580R13TAXIMHM05']</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>2949</v>
+        <v>2313</v>
       </c>
       <c r="E146" t="n">
         <v>2</v>
@@ -3793,21 +3781,21 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1325114812074TUHL0</t>
+          <t>1225219015010QSTL0</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>['C14580R12UHLTHMI05', 'B1458012UHLIFHMI01']</t>
+          <t>['B195R15STLKNGHMI04', 'B195R15STLKINGHM01']</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1213</v>
+        <v>2705</v>
       </c>
       <c r="E147" t="n">
         <v>2</v>
@@ -3816,21 +3804,21 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1325114812074TUHL0</t>
+          <t>1D25212812086FXPC0</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>['B1458012ULHLIFGC03', 'B1458012ULHLIFHM01']</t>
+          <t>['B1208012ULXPCHMI06', 'B1208012ULXPCHMI03']</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2269</v>
+        <v>586</v>
       </c>
       <c r="E148" t="n">
         <v>2</v>
@@ -3839,21 +3827,21 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9410</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1D25214012008QSTL0</t>
+          <t>1325217514082TVECH</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>['B14512STKINGLHMI02', 'B14512STKINGLHMI01']</t>
+          <t>['B1756514VECTRAGC11', 'B1756514VECTRAGC10']</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2977</v>
+        <v>2790</v>
       </c>
       <c r="E149" t="n">
         <v>2</v>
@@ -3862,7 +3850,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3872,11 +3860,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>['B1208012ULTXPCHM02', 'B1208012ULTXPCHM01']</t>
+          <t>['B1208012ULXPCHMI10', 'B1208012ULXPCHMI04']</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>2267</v>
+        <v>640</v>
       </c>
       <c r="E150" t="n">
         <v>2</v>
@@ -3885,7 +3873,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3895,11 +3883,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>['B1208012ULXPCHMI06', 'B1208012ULXPCHMI03']</t>
+          <t>['B1208012ULXPCHMI07', 'B1208012ULXPCHMI05']</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>2977</v>
+        <v>1190</v>
       </c>
       <c r="E151" t="n">
         <v>2</v>
@@ -3908,21 +3896,21 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1D25212812074FXC10</t>
+          <t>1325221715100SRXT0</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>['B1208012ULXPC1GC03', 'B1208012ULXPC1GC01']</t>
+          <t>['B2157515RAXATHMI04', 'B2157515RANXATTY02']</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1221</v>
+        <v>2530</v>
       </c>
       <c r="E152" t="n">
         <v>2</v>
@@ -3931,21 +3919,21 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1D25212812086FXPC0</t>
+          <t>1325214812074TUHL0</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>['B1208012ULXPCHMI07', 'B1208012ULXPCHMI05']</t>
+          <t>['C14580R12UHLTHMI05', 'B1458012UHLIFHMI01']</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>2248</v>
       </c>
       <c r="E153" t="n">
         <v>2</v>
@@ -3954,21 +3942,21 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1D25213812090FXPC0</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>['B70015STKINGLHMI20', 'B70015STKINGLHMI19']</t>
+          <t>['B13080R12ULXPCGC03', 'B13080R12UXPCHMI02']</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2801</v>
+        <v>2022</v>
       </c>
       <c r="E154" t="n">
         <v>2</v>
@@ -3977,21 +3965,21 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1325121715115SLTB0</t>
+          <t>1D25213812090FXPC0</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>['B2157515BRULTHMI02', 'B2157515BRULTHMI01']</t>
+          <t>['B13080R12UXPCHMI08', 'B13080R12ULXPCGC01']</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2935</v>
+        <v>2203</v>
       </c>
       <c r="E155" t="n">
         <v>2</v>
@@ -4000,21 +3988,21 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1325119815106QBRQ0</t>
+          <t>1325214812074TUHL0</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>['B1958015BRUTLTHM05', 'B1958015BRUTLTHM04']</t>
+          <t>['C14580R12UHLTHMI06', 'B1458012UHLIFHMI02']</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2541</v>
+        <v>2116</v>
       </c>
       <c r="E156" t="n">
         <v>2</v>
@@ -4023,21 +4011,21 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1D25213812090FXPC0</t>
+          <t>1D25212812074FXC10</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>['B13080R12ULXPCGC03', 'B13080R12UXPCHMI02']</t>
+          <t>['B1208012ULXPC1GC05', 'B1208012UXPC1HMI01']</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1315</v>
+        <v>448</v>
       </c>
       <c r="E157" t="n">
         <v>2</v>
@@ -4046,21 +4034,21 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1D25213812090FXPC0</t>
+          <t>1D25212812074FXC10</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>['B13080R12UXPCHMI08', 'B13080R12ULXPCGC01']</t>
+          <t>['B1208012UXPC1HMI02', 'B1208012ULXPC1GC04']</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1743</v>
+        <v>274</v>
       </c>
       <c r="E158" t="n">
         <v>2</v>
@@ -4069,21 +4057,21 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1325114812074TUHL0</t>
+          <t>1D25212812074FXC10</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>['C14580R12UHLTHMI06', 'B1458012UHLIFHMI02']</t>
+          <t>['B1208012ULXPC1GC09', 'B1208012ULXPC1GC06']</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2960</v>
+        <v>134</v>
       </c>
       <c r="E159" t="n">
         <v>2</v>
@@ -4092,21 +4080,21 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1D25212812074FXC10</t>
+          <t>1225170015012LSTL0</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>['B1208012ULXPC1GC05', 'B1208012UXPC1HMI01']</t>
+          <t>['B70015STKINGLTHM46', 'B70015STKINGLTHM30']</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>2919</v>
+        <v>1491</v>
       </c>
       <c r="E160" t="n">
         <v>2</v>
@@ -4115,21 +4103,21 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1D25212812074FXC10</t>
+          <t>1225221715115SSTL0</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>['B1208012UXPC1HMI02', 'B1208012ULXPC1GC04']</t>
+          <t>['B2157515STLKNGHM13', 'B2157515STLKGHMI05']</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>2708</v>
+        <v>2571</v>
       </c>
       <c r="E161" t="n">
         <v>2</v>
@@ -4138,21 +4126,21 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1D25212812074FXC10</t>
+          <t>1225170015012LSTL0</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>['B1208012ULXPC1GC09', 'B1208012ULXPC1GC06']</t>
+          <t>['B70015STKINGLTHM32', 'B70015STKINGLTHM31']</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>2555</v>
+        <v>1522</v>
       </c>
       <c r="E162" t="n">
         <v>2</v>
@@ -4161,7 +4149,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4171,11 +4159,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM46', 'B70015STKINGLTHM30']</t>
+          <t>['B70015STKINGLTHM24', 'B70015STKINGLTHM22']</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>2888</v>
+        <v>1780</v>
       </c>
       <c r="E163" t="n">
         <v>2</v>
@@ -4184,21 +4172,21 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>1225170015010LSTL0</t>
+          <t>1325216814085STMX0</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM11', 'B70015STKINGLTHM17']</t>
+          <t>['B1658014TAXIMXHM03', 'B1658014TAXIMXHM02']</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>2034</v>
+        <v>2398</v>
       </c>
       <c r="E164" t="n">
         <v>2</v>
@@ -4207,92 +4195,23 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1225170015012LSTL0</t>
+          <t>1325216814085STMX0</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>['B70015STKINGLTHM31', 'B70015STKINGLTHM32']</t>
+          <t>['B1658014TAXIMXHM05', 'B1658014TAXIMXGC04']</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>2961</v>
+        <v>2648</v>
       </c>
       <c r="E165" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>9704</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>1225170015012LSTL0</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>['B70015STKINGLTHM24', 'B70015STKINGLTHM22']</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>7</v>
-      </c>
-      <c r="E166" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>9802</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>1325216814085STMX0</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>['B1658014TAXIMXHM03', 'B1658014TAXIMXHM02']</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>1689</v>
-      </c>
-      <c r="E167" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>9804</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>1325216814085STMX0</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>['B1658014TAXIMXGC04', 'B1658014TAXIMXGC02']</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>1916</v>
-      </c>
-      <c r="E168" t="n">
         <v>2</v>
       </c>
     </row>
